--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_09-06-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_09-06-2025.xlsx
@@ -1063,7 +1063,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>£23.15</t>
+          <t>£23.16</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>£27.45</t>
+          <t>£27.46</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>£28.60</t>
+          <t>£28.61</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>£43.26</t>
+          <t>£43.27</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>£42.15</t>
+          <t>£42.16</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>£1407.12</t>
+          <t>£1407.24</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>£29.81</t>
+          <t>£29.82</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/celotex-pl4025-ins-plasterboard-25mm-12-5mm (Caused by SSLError(SSLEOFError(8, '[SSL: UNEXPECTED_EOF_WHILE_READING] EOF occurred in violation of protocol (_ssl.c:1006)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>£40.20</t>
+          <t>£40.21</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/celotex-pl4050-ins-plasterboard-50mm-12-5mm (Caused by SSLError(SSLEOFError(8, '[SSL: UNEXPECTED_EOF_WHILE_READING] EOF occurred in violation of protocol (_ssl.c:1006)')))</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>£44.51</t>
+          <t>£44.52</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2645,7 +2645,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/celotex-cavity-insulation-cw4050-450mm-x-1200mm-pack-of-11 (Caused by SSLError(SSLEOFError(8, '[SSL: UNEXPECTED_EOF_WHILE_READING] EOF occurred in violation of protocol (_ssl.c:1006)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
